--- a/ARMP_Demo_Invoices_1000.xlsx
+++ b/ARMP_Demo_Invoices_1000.xlsx
@@ -30421,10 +30421,10 @@
     </row>
     <row r="791">
       <c r="A791" t="str">
-        <v>40200100</v>
+        <v>40200101</v>
       </c>
       <c r="B791" t="str">
-        <v>Beacon Medical Supply Co</v>
+        <v>Northlight Electronics Corp</v>
       </c>
       <c r="C791" t="str">
         <v>9100000790</v>
